--- a/mode_docx_gen/pmi_ka/ksv2_modes/КСВ_11.xlsx
+++ b/mode_docx_gen/pmi_ka/ksv2_modes/КСВ_11.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -1110,8 +1110,8 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1155,8 +1155,8 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
+      <c r="W2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1634,9 +1634,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
